--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\airib\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2F2AF75-546F-4D6B-BF3B-26674EC25F58}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="10575" yWindow="1890" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>日付</t>
   </si>
@@ -60,6 +60,21 @@
   </si>
   <si>
     <t>reset_index, チェーン</t>
+  </si>
+  <si>
+    <t>Streamlit, Plotly, pandas, health_dashboard</t>
+  </si>
+  <si>
+    <t>df_filtered絞り込み順, dtアクセサー, 変数名ミス</t>
+  </si>
+  <si>
+    <t>✅ KPIカード・グラフ・フィルター完成
+✅ サイドバー移動
+✅ 月別平均歩数グラフ
+✅ 全グラフカラー統一</t>
+  </si>
+  <si>
+    <t>value_counts/reset_index/Series/df_filtered上書き/Streamlit再実行</t>
   </si>
 </sst>
 </file>
@@ -105,12 +120,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -445,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -493,6 +511,43 @@
         <v>10</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B3">
+        <v>208</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2F2AF75-546F-4D6B-BF3B-26674EC25F58}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE784161-68FE-4698-BD74-416B2173FBD6}"/>
   <bookViews>
-    <workbookView xWindow="10575" yWindow="1890" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="9705" yWindow="1590" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>日付</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>value_counts/reset_index/Series/df_filtered上書き/Streamlit再実行</t>
+  </si>
+  <si>
+    <t>st.cache_data, サイドバーフィルター, st.metric, px.line, px.bar, st.columns, with構文, groupby, fstring書式, update_traces, python -m</t>
+  </si>
+  <si>
+    <t>groupby後の列名, update_tracesの順番, col4未定義エラー</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -535,6 +541,9 @@
       <c r="A4" s="2">
         <v>46093</v>
       </c>
+      <c r="B4">
+        <v>187</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
@@ -546,6 +555,26 @@
       </c>
       <c r="F4">
         <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5">
+        <v>180</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE784161-68FE-4698-BD74-416B2173FBD6}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24FDFA04-9FB8-48F5-815C-7FF814C191E6}"/>
   <bookViews>
-    <workbookView xWindow="9705" yWindow="1590" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="6540" yWindow="2310" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>日付</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>groupby後の列名, update_tracesの順番, col4未定義エラー</t>
+  </si>
+  <si>
+    <t>Kaggle pandas Lesson 1〜2途中（Creating/Reading/Writing, Indexing/Selecting）、Mood Dashboardバグ修正</t>
+  </si>
+  <si>
+    <t>loc/iloc の範囲指定の違い、encodingの不一致、日付型の混在</t>
   </si>
 </sst>
 </file>
@@ -469,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -577,6 +583,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24FDFA04-9FB8-48F5-815C-7FF814C191E6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{207209D0-90A8-4C44-AB32-02AB526007C5}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="2310" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="30135" yWindow="2850" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>日付</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>loc/iloc の範囲指定の違い、encodingの不一致、日付型の混在</t>
+  </si>
+  <si>
+    <t>Kaggle Lesson 2「Indexing, Selecting &amp; Assigning」/ Anki復習（pd.cut, orientation, barmode等）</t>
+  </si>
+  <si>
+    <t>locとilocの範囲の違い、(0, 5000]の記号の意味、barmode="group"のデフォルト</t>
   </si>
 </sst>
 </file>
@@ -156,6 +162,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -603,6 +613,26 @@
         <v>15</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>46096</v>
+      </c>
+      <c r="B7">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{207209D0-90A8-4C44-AB32-02AB526007C5}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C7C1FB-0FFC-40A8-A1F9-FAEDF65F5E31}"/>
   <bookViews>
-    <workbookView xWindow="30135" yWindow="2850" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>日付</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>locとilocの範囲の違い、(0, 5000]の記号の意味、barmode="group"のデフォルト</t>
+  </si>
+  <si>
+    <t>Kaggle Learn pandas Lesson 3 エクササイズ</t>
+  </si>
+  <si>
+    <t>axis='columns'の意味、row.pointsとrowの違い、apply()の使い方</t>
   </si>
 </sst>
 </file>
@@ -162,10 +168,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -633,6 +635,26 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B8">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C7C1FB-0FFC-40A8-A1F9-FAEDF65F5E31}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38681BC6-9E74-498F-A0AF-D3A25A8340C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="9195" yWindow="1725" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>日付</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>axis='columns'の意味、row.pointsとrowの違い、apply()の使い方</t>
+  </si>
+  <si>
+    <t>Kaggle Learn pandas Lesson 6前半（Renaming &amp; Combining）</t>
+  </si>
+  <si>
+    <t>rename_axis()の概念</t>
   </si>
 </sst>
 </file>
@@ -487,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -655,6 +661,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>46098</v>
+      </c>
+      <c r="B9">
+        <v>172</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_record.xlsx
+++ b/study_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6740a86ead1e19c5/ドキュメント/study record/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38681BC6-9E74-498F-A0AF-D3A25A8340C6}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{2E009108-6E56-4DA6-A727-21F2A6A95E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{665A0E5C-EF6B-4245-A3A7-649B06D589C1}"/>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="1725" windowWidth="17970" windowHeight="13635" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
+    <workbookView xWindow="9135" yWindow="1920" windowWidth="17970" windowHeight="13485" xr2:uid="{9C5CAC8C-D54E-4523-A34E-1A463A43B8BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>日付</t>
   </si>
@@ -105,6 +105,24 @@
   </si>
   <si>
     <t>rename_axis()の概念</t>
+  </si>
+  <si>
+    <t>Kaggle Learn pandas Lesson 6後半・エクササイズ全問・コース完全修了🎉</t>
+  </si>
+  <si>
+    <t>rename_axis()の復習</t>
+  </si>
+  <si>
+    <t>Kaggle pandas総合ドリル Level1〜3（iloc, 複数条件フィルタ, 欠損値, groupby, agg, apply, rename, concat）</t>
+  </si>
+  <si>
+    <t>ilocスライスの終端、apply列指定忘れ、aggのクォート忘れ</t>
+  </si>
+  <si>
+    <t>pandas総合ドリル Level1〜5 / lambda・メソッドチェーン・count系特訓</t>
+  </si>
+  <si>
+    <t>lambda・複数条件の()・applyとmapの違い・fillnaに辞書を渡す</t>
   </si>
 </sst>
 </file>
@@ -174,6 +192,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -493,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C896B3-AFDD-4D97-9B8D-FB17D578DFA4}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -681,6 +703,66 @@
         <v>6</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B10">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B11">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
